--- a/output/pdf_financials_xlsx/TELO.xlsx
+++ b/output/pdf_financials_xlsx/TELO.xlsx
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.099345</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -14289,7 +14289,11 @@
           <t>Share-based payment reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.099345</v>
       </c>

--- a/output/pdf_financials_xlsx/TELO.xlsx
+++ b/output/pdf_financials_xlsx/TELO.xlsx
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.008522999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003119</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.037191</v>
+        <v>-0.045714</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.10873</v>
+        <v>-0.111849</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.434402</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.037191</v>
+        <v>-0.045714</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.10873</v>
+        <v>-0.111849</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.413353</v>
@@ -2050,28 +2050,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.506698</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.459929</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.261417</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.038663</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.200395</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.067331</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.019495</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.920983</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.636502</v>
@@ -2083,10 +2083,10 @@
         <v>2.673247</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.7960199999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.789293</v>
       </c>
     </row>
     <row r="35">
@@ -2142,28 +2142,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.506698</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.459929</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.261417</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.038663</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.200395</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.067331</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.019495</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.920983</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>3.636502</v>
@@ -2175,10 +2175,10 @@
         <v>2.673247</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.7960199999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.789293</v>
       </c>
     </row>
     <row r="37">
@@ -2694,28 +2694,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.506698</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.459929</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.286875</v>
+        <v>0.025458</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.08297599999999999</v>
+        <v>0.044313</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.866111</v>
+        <v>0.665716</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.126362</v>
+        <v>0.059031</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.046356</v>
+        <v>0.026861</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.988044</v>
+        <v>0.067061</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.027536</v>
@@ -2727,10 +2727,10 @@
         <v>0.105934</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.887784</v>
+        <v>0.091764</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.865723</v>
+        <v>0.07643</v>
       </c>
     </row>
     <row r="49">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E327" s="5" t="n">

--- a/output/pdf_financials_xlsx/TELO.xlsx
+++ b/output/pdf_financials_xlsx/TELO.xlsx
@@ -1772,28 +1772,28 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.124326</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.082909</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.064719</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.062228</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.056956</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.033114</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.039536</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.014452</v>
       </c>
     </row>
     <row r="29">
@@ -1820,28 +1820,28 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.694618</v>
+        <v>-4.570292</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.074192</v>
+        <v>-0.991283</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.241696</v>
+        <v>-1.176977</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.069963</v>
+        <v>-1.007735</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.110454</v>
+        <v>-2.053498</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.820772</v>
+        <v>-2.787658</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.71301</v>
+        <v>-2.673474</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.718753</v>
+        <v>-2.704301</v>
       </c>
     </row>
     <row r="30">
@@ -5159,31 +5159,31 @@
         <v>0.074088</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.110358</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.124326</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.082909</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.064719</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.062228</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.056956</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.033114</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.039536</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.014452</v>
       </c>
     </row>
     <row r="101">
@@ -14619,7 +14619,11 @@
           <t>Depreciation of property and equipment 6,11</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -17178,7 +17182,11 @@
           <t>Depreciation of property and equipment 7,12</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -18450,7 +18458,11 @@
           <t>Depreciation of property and equipment 7,13</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -19505,7 +19517,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -21633,7 +21649,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -22694,7 +22714,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -22775,7 +22799,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">

--- a/output/pdf_financials_xlsx/TELO.xlsx
+++ b/output/pdf_financials_xlsx/TELO.xlsx
@@ -5659,16 +5659,16 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004663</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.144584</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.254025</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023167</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -5889,13 +5889,13 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.317031</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.266173</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.223694</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.008671</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -6751,16 +6751,16 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004663</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.144584</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.254025</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023167</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -6797,16 +6797,16 @@
         <v>-0.106769</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.156536</v>
+        <v>-0.161199</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.8393080000000001</v>
+        <v>-0.983892</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-7.899863</v>
+        <v>-8.153888</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-3.206441</v>
+        <v>-3.229608</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.327836</v>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -22058,7 +22058,11 @@
           <t>Purchases of equipment 7</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -23927,7 +23931,11 @@
           <t>Purchases of equipment 8</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -24006,7 +24014,11 @@
           <t>Purchases of intangible assets 9</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -25786,7 +25798,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -25865,7 +25881,11 @@
           <t>Purchases of intangible assets</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
